--- a/outputs/203-15.xlsx
+++ b/outputs/203-15.xlsx
@@ -230,35 +230,35 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -526,7 +526,7 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.88"/>
   </cols>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -558,7 +558,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1111</v>
       </c>
@@ -590,7 +590,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="n">
         <v>1111</v>
       </c>
@@ -622,7 +622,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="3" t="n">
         <v>1111</v>
       </c>
@@ -654,7 +654,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="n">
         <v>1111</v>
       </c>
@@ -686,7 +686,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="n">
         <v>1111</v>
       </c>
@@ -718,7 +718,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="6" t="n">
         <v>2222</v>
       </c>
@@ -750,7 +750,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="6" t="n">
         <v>2222</v>
       </c>
@@ -782,7 +782,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="6" t="n">
         <v>2222</v>
       </c>
@@ -814,7 +814,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="6" t="n">
         <v>2222</v>
       </c>
@@ -846,7 +846,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="6" t="n">
         <v>2222</v>
       </c>
@@ -900,7 +900,7 @@
   <dimension ref="A1:M3"/>
   <sheetFormatPr defaultColWidth="13" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -941,7 +941,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="3" t="n">
         <v>1111</v>
       </c>
@@ -983,7 +983,7 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
         <v>2222</v>
       </c>

--- a/outputs/203-15.xlsx
+++ b/outputs/203-15.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="28">
   <si>
     <t xml:space="preserve">staff no.</t>
   </si>
@@ -105,33 +105,20 @@
   </si>
   <si>
     <t xml:space="preserve">US</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Transport Allowance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Other Allowance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Social Allowance</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="2">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
-    <numFmt numFmtId="165" formatCode="#,##0.00"/>
   </numFmts>
-  <fonts count="5">
+  <fonts count="4">
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <charset val="1"/>
     </font>
@@ -150,53 +137,21 @@
       <name val="Arial"/>
       <family val="0"/>
     </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF222222"/>
-      <name val="Arial"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC0C0C0"/>
-        <bgColor rgb="FFCCCCFF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor rgb="FFFFFF00"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor rgb="FFC0C0C0"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -225,40 +180,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="165" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="top" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -271,71 +198,11 @@
     <cellStyle name="Currency [0]" xfId="18" builtinId="7"/>
     <cellStyle name="Percent" xfId="19" builtinId="5"/>
   </cellStyles>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="FF000000"/>
-      <rgbColor rgb="FFFFFFFF"/>
-      <rgbColor rgb="FFFF0000"/>
-      <rgbColor rgb="FF00FF00"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008000"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FF808000"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FFC0C0C0"/>
-      <rgbColor rgb="FF808080"/>
-      <rgbColor rgb="FF9999FF"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FFFFFFCC"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FF660066"/>
-      <rgbColor rgb="FFFF8080"/>
-      <rgbColor rgb="FF0066CC"/>
-      <rgbColor rgb="FFCCCCFF"/>
-      <rgbColor rgb="FF000080"/>
-      <rgbColor rgb="FFFF00FF"/>
-      <rgbColor rgb="FFFFFF00"/>
-      <rgbColor rgb="FF00FFFF"/>
-      <rgbColor rgb="FF800080"/>
-      <rgbColor rgb="FF800000"/>
-      <rgbColor rgb="FF008080"/>
-      <rgbColor rgb="FF0000FF"/>
-      <rgbColor rgb="FF00CCFF"/>
-      <rgbColor rgb="FFCCFFFF"/>
-      <rgbColor rgb="FFCCFFCC"/>
-      <rgbColor rgb="FFFFFF99"/>
-      <rgbColor rgb="FF99CCFF"/>
-      <rgbColor rgb="FFFF99CC"/>
-      <rgbColor rgb="FFCC99FF"/>
-      <rgbColor rgb="FFFFCC99"/>
-      <rgbColor rgb="FF3366FF"/>
-      <rgbColor rgb="FF33CCCC"/>
-      <rgbColor rgb="FF92D050"/>
-      <rgbColor rgb="FFFFCC00"/>
-      <rgbColor rgb="FFFF9900"/>
-      <rgbColor rgb="FFFF6600"/>
-      <rgbColor rgb="FF666699"/>
-      <rgbColor rgb="FF969696"/>
-      <rgbColor rgb="FF003366"/>
-      <rgbColor rgb="FF339966"/>
-      <rgbColor rgb="FF003300"/>
-      <rgbColor rgb="FF333300"/>
-      <rgbColor rgb="FF993300"/>
-      <rgbColor rgb="FF993366"/>
-      <rgbColor rgb="FF333399"/>
-      <rgbColor rgb="FF222222"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office 主题​​">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -345,44 +212,44 @@
         <a:srgbClr val="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="44546A"/>
+        <a:srgbClr val="1F497D"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E7E6E6"/>
+        <a:srgbClr val="EEECE1"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="4472C4"/>
+        <a:srgbClr val="4F81BD"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="ED7D31"/>
+        <a:srgbClr val="C0504D"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="A5A5A5"/>
+        <a:srgbClr val="9BBB59"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="FFC000"/>
+        <a:srgbClr val="8064A2"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="5B9BD5"/>
+        <a:srgbClr val="4BACC6"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="70AD47"/>
+        <a:srgbClr val="F79646"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="0563C1"/>
+        <a:srgbClr val="0000FF"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="954F72"/>
+        <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Calibri Light" panose="020F0302020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Cambria" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204" pitchFamily="0" charset="1"/>
+        <a:latin typeface="Calibri" pitchFamily="0" charset="1"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
       </a:minorFont>
@@ -396,63 +263,54 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="110000"/>
-                <a:tint val="67000"/>
+                <a:tint val="50000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="35000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="73000"/>
+                <a:tint val="37000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="105000"/>
-                <a:tint val="81000"/>
+                <a:tint val="15000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="1"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:lumMod val="102000"/>
-                <a:tint val="94000"/>
+                <a:shade val="51000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="80000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="93000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:lumMod val="99000"/>
-                <a:shade val="78000"/>
+                <a:shade val="94000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:lin ang="16200000" scaled="0"/>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
-        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
-        <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
+        <a:ln w="38100" cap="flat" cmpd="sng" algn="ctr">
           <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
         </a:ln>
       </a:lnStyleLst>
       <a:effectStyleLst>
@@ -470,34 +328,46 @@
         <a:solidFill>
           <a:schemeClr val="phClr"/>
         </a:solidFill>
-        <a:solidFill>
-          <a:schemeClr val="phClr">
-            <a:tint val="95000"/>
-          </a:schemeClr>
-        </a:solidFill>
         <a:gradFill>
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="93000"/>
-                <a:shade val="98000"/>
-                <a:lumMod val="102000"/>
+                <a:tint val="40000"/>
               </a:schemeClr>
             </a:gs>
-            <a:gs pos="50000">
+            <a:gs pos="40000">
               <a:schemeClr val="phClr">
-                <a:tint val="98000"/>
-                <a:shade val="90000"/>
-                <a:lumMod val="103000"/>
+                <a:tint val="45000"/>
+                <a:shade val="99000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:shade val="63000"/>
+                <a:shade val="20000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
-          <a:lin ang="5400000" scaled="0"/>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="-80000" r="50000" b="180000"/>
+          </a:path>
+          <a:tileRect l="0" t="0" r="0" b="0"/>
+        </a:gradFill>
+        <a:gradFill>
+          <a:gsLst>
+            <a:gs pos="0">
+              <a:schemeClr val="phClr">
+                <a:tint val="80000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="100000">
+              <a:schemeClr val="phClr">
+                <a:shade val="30000"/>
+              </a:schemeClr>
+            </a:gs>
+          </a:gsLst>
+          <a:path path="circle">
+            <a:fillToRect l="50000" t="50000" r="50000" b="50000"/>
+          </a:path>
           <a:tileRect l="0" t="0" r="0" b="0"/>
         </a:gradFill>
       </a:bgFillStyleLst>
@@ -511,380 +381,365 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="8.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="10.11"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="11.66"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="18.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="7.56"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="10.89"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="20.33"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="18"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="10" min="10" style="1" width="8.88"/>
-  </cols>
+  <dimension ref="A1:J11"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>1111</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G2" s="3" t="s">
+      <c r="G2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H2" s="3" t="s">
+      <c r="H2" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I2" s="4" t="n">
+      <c r="I2" s="1" t="n">
         <v>5000</v>
       </c>
-      <c r="J2" s="5" t="s">
+      <c r="J2" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A3" s="1" t="n">
         <v>1111</v>
       </c>
-      <c r="B3" s="3" t="s">
+      <c r="B3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="1" t="n">
         <v>2000</v>
       </c>
-      <c r="J3" s="5" t="s">
+      <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
         <v>1111</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E4" s="3" t="s">
+      <c r="E4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H4" s="3" t="s">
+      <c r="H4" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I4" s="4" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J4" s="5" t="s">
+      <c r="I4" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J4" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
         <v>1111</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="E5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="3" t="s">
+      <c r="H5" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="1" t="n">
         <v>1750</v>
       </c>
-      <c r="J5" s="5" t="s">
+      <c r="J5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
         <v>1111</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D6" s="3" t="s">
+      <c r="D6" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E6" s="3" t="s">
+      <c r="E6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F6" s="3" t="s">
+      <c r="F6" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="H6" s="3" t="s">
+      <c r="H6" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="J6" s="5" t="s">
+      <c r="J6" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="6" t="n">
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
         <v>2222</v>
       </c>
-      <c r="B7" s="6" t="s">
+      <c r="B7" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C7" s="6" t="s">
+      <c r="C7" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D7" s="6" t="s">
+      <c r="D7" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="E7" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F7" s="6" t="s">
+      <c r="F7" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H7" s="6" t="s">
+      <c r="H7" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="I7" s="7" t="n">
+      <c r="I7" s="1" t="n">
         <v>4000</v>
       </c>
-      <c r="J7" s="5" t="s">
+      <c r="J7" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="6" t="n">
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
         <v>2222</v>
       </c>
-      <c r="B8" s="6" t="s">
+      <c r="B8" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C8" s="6" t="s">
+      <c r="C8" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D8" s="6" t="s">
+      <c r="D8" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E8" s="6" t="s">
+      <c r="E8" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F8" s="6" t="s">
+      <c r="F8" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H8" s="6" t="s">
+      <c r="H8" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J8" s="5" t="s">
+      <c r="I8" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J8" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="6" t="n">
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
         <v>2222</v>
       </c>
-      <c r="B9" s="6" t="s">
+      <c r="B9" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C9" s="6" t="s">
+      <c r="C9" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="6" t="s">
+      <c r="D9" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E9" s="6" t="s">
+      <c r="E9" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F9" s="6" t="s">
+      <c r="F9" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H9" s="6" t="s">
+      <c r="H9" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="I9" s="7" t="n">
-        <v>1500</v>
-      </c>
-      <c r="J9" s="5" t="s">
+      <c r="I9" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="J9" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="6" t="n">
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
         <v>2222</v>
       </c>
-      <c r="B10" s="6" t="s">
+      <c r="B10" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="6" t="s">
+      <c r="C10" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D10" s="6" t="s">
+      <c r="D10" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E10" s="6" t="s">
+      <c r="E10" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F10" s="6" t="s">
+      <c r="F10" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H10" s="6" t="s">
+      <c r="H10" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="I10" s="7" t="n">
+      <c r="I10" s="1" t="n">
         <v>1250</v>
       </c>
-      <c r="J10" s="5" t="s">
+      <c r="J10" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="6" t="n">
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
         <v>2222</v>
       </c>
-      <c r="B11" s="6" t="s">
+      <c r="B11" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="C11" s="6" t="s">
+      <c r="C11" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D11" s="6" t="s">
+      <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="6" t="s">
+      <c r="E11" s="1" t="s">
         <v>25</v>
       </c>
-      <c r="F11" s="6" t="s">
+      <c r="F11" s="1" t="s">
         <v>26</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="H11" s="6" t="s">
+      <c r="H11" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="I11" s="7" t="n">
+      <c r="I11" s="1" t="n">
         <v>250</v>
       </c>
-      <c r="J11" s="5" t="s">
+      <c r="J11" s="1" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="B14" s="8"/>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
@@ -897,71 +752,50 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:M3"/>
-  <sheetFormatPr defaultColWidth="13" defaultRowHeight="13.5" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:M11"/>
+  <sheetFormatPr defaultColWidth="8.5390625" defaultRowHeight="15" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2" t="s">
+    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
       <c r="G1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="I1" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="J1" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="K1" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="L1" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="M1" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
+    </row>
+    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
         <v>1111</v>
       </c>
-      <c r="B2" s="3" t="s">
+      <c r="B2" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="C2" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="3" t="s">
+      <c r="E2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="F2" s="3" t="s">
+      <c r="F2" s="1" t="s">
         <v>14</v>
-      </c>
-      <c r="G2" s="1" t="s">
-        <v>15</v>
       </c>
       <c r="H2" s="1" t="n">
         <v>5000</v>
@@ -983,52 +817,361 @@
         <v>10500</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="n">
-        <v>2222</v>
+        <v>1111</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>24</v>
+        <v>12</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>26</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
       <c r="H3" s="1" t="n">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="I3" s="1" t="n">
-        <v>1500</v>
+        <v>2000</v>
       </c>
       <c r="J3" s="1" t="n">
         <v>1500</v>
       </c>
       <c r="K3" s="1" t="n">
-        <v>1250</v>
+        <v>1750</v>
       </c>
       <c r="L3" s="1" t="n">
         <v>250</v>
       </c>
       <c r="M3" s="1" t="n">
         <f aca="false">SUM(H3:L3)</f>
-        <v>8500</v>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A4" s="1" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F4" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I4" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J4" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K4" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L4" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M4" s="1" t="n">
+        <f aca="false">SUM(H4:L4)</f>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A5" s="1" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B5" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C5" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H5" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I5" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J5" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K5" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L5" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M5" s="1" t="n">
+        <f aca="false">SUM(H5:L5)</f>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A6" s="1" t="n">
+        <v>1111</v>
+      </c>
+      <c r="B6" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C6" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J6" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K6" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L6" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M6" s="1" t="n">
+        <f aca="false">SUM(H6:L6)</f>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A7" s="1" t="n">
+        <v>2222</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C7" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E7" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H7" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I7" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J7" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K7" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L7" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M7" s="1" t="n">
+        <f aca="false">SUM(H7:L7)</f>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A8" s="1" t="n">
+        <v>2222</v>
+      </c>
+      <c r="B8" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C8" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E8" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H8" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I8" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J8" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K8" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L8" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M8" s="1" t="n">
+        <f aca="false">SUM(H8:L8)</f>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A9" s="1" t="n">
+        <v>2222</v>
+      </c>
+      <c r="B9" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C9" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H9" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I9" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J9" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K9" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L9" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M9" s="1" t="n">
+        <f aca="false">SUM(H9:L9)</f>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A10" s="1" t="n">
+        <v>2222</v>
+      </c>
+      <c r="B10" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C10" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H10" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I10" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J10" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K10" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L10" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M10" s="1" t="n">
+        <f aca="false">SUM(H10:L10)</f>
+        <v>10500</v>
+      </c>
+    </row>
+    <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A11" s="1" t="n">
+        <v>2222</v>
+      </c>
+      <c r="B11" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C11" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="H11" s="1" t="n">
+        <v>5000</v>
+      </c>
+      <c r="I11" s="1" t="n">
+        <v>2000</v>
+      </c>
+      <c r="J11" s="1" t="n">
+        <v>1500</v>
+      </c>
+      <c r="K11" s="1" t="n">
+        <v>1750</v>
+      </c>
+      <c r="L11" s="1" t="n">
+        <v>250</v>
+      </c>
+      <c r="M11" s="1" t="n">
+        <f aca="false">SUM(H11:L11)</f>
+        <v>10500</v>
       </c>
     </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
+  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
   <headerFooter differentFirst="false" differentOddEven="false">
     <oddHeader/>
     <oddFooter/>
